--- a/STE_EXTRAS.xlsx
+++ b/STE_EXTRAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rebel\OneDrive\Documents\Projects\STE-feature-clean-code-assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90296B4E-C411-4AA8-9050-77C1F56DDD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE695E50-91A1-4195-8AE5-A3B310CFC1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4800" yWindow="1350" windowWidth="14400" windowHeight="8722" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="99">
   <si>
     <t>Designation</t>
   </si>
@@ -101,30 +101,18 @@
     <t>DP 01</t>
   </si>
   <si>
-    <t>Desk Table</t>
-  </si>
-  <si>
     <t>DP 03</t>
   </si>
   <si>
     <t>Glass Round Table</t>
   </si>
   <si>
-    <t>1m dia x .75m</t>
-  </si>
-  <si>
     <t>DP 04</t>
   </si>
   <si>
-    <t>White Chair</t>
-  </si>
-  <si>
     <t>DP 05</t>
   </si>
   <si>
-    <t>Cushioned Chair</t>
-  </si>
-  <si>
     <t>DP 08</t>
   </si>
   <si>
@@ -134,15 +122,9 @@
     <t>DP 09</t>
   </si>
   <si>
-    <t>Sofa Double Seat</t>
-  </si>
-  <si>
     <t>DP 10</t>
   </si>
   <si>
-    <t>Sofa Three Seat</t>
-  </si>
-  <si>
     <t>DP 11</t>
   </si>
   <si>
@@ -188,9 +170,6 @@
     <t>DP 27</t>
   </si>
   <si>
-    <t>Garment Stand</t>
-  </si>
-  <si>
     <t>INR Rates Listed</t>
   </si>
   <si>
@@ -209,19 +188,10 @@
     <t>Rate Basis</t>
   </si>
   <si>
-    <t>1m x .5m x .75m</t>
-  </si>
-  <si>
     <t>Per day</t>
   </si>
   <si>
-    <t>Brochure Rack</t>
-  </si>
-  <si>
     <t>1m x .25m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plasma with Stand 32 INCH </t>
   </si>
   <si>
     <r>
@@ -236,6 +206,147 @@
       </rPr>
       <t>NOTE REFRENCE IMAGES ARE THERE .FINAL PRODUCT COULD CHANGE )</t>
     </r>
+  </si>
+  <si>
+    <t>System Table (Desk Table)</t>
+  </si>
+  <si>
+    <t>1m*0.5m*0.75m ht</t>
+  </si>
+  <si>
+    <t>DP 02</t>
+  </si>
+  <si>
+    <t>Wooden Table with cover</t>
+  </si>
+  <si>
+    <t>5'x2.5'</t>
+  </si>
+  <si>
+    <t>2'8" Ø &amp; 2'6"ht</t>
+  </si>
+  <si>
+    <t>Exhibition Chairs (White Chair)</t>
+  </si>
+  <si>
+    <t>Standard exhibition seating</t>
+  </si>
+  <si>
+    <t>Stake Chair (Cushioned Chair)</t>
+  </si>
+  <si>
+    <t>Cushioned conference chair</t>
+  </si>
+  <si>
+    <t>DP 06</t>
+  </si>
+  <si>
+    <t>Apple chair</t>
+  </si>
+  <si>
+    <t>Modern designer seating</t>
+  </si>
+  <si>
+    <t>Plush armchair</t>
+  </si>
+  <si>
+    <t>2 Seater Sofa (Sofa Double Seat)</t>
+  </si>
+  <si>
+    <t>2-seater luxury lounge sofa</t>
+  </si>
+  <si>
+    <t>3 Seater Sofa (Sofa Three Seat)</t>
+  </si>
+  <si>
+    <t>3-seater spacious lounge sofa</t>
+  </si>
+  <si>
+    <t>Rectangle Tipoi (Glass Centre Table)</t>
+  </si>
+  <si>
+    <t>Glass top lounge center table</t>
+  </si>
+  <si>
+    <t>DP 12</t>
+  </si>
+  <si>
+    <t>Display Glass Counter Show case (without lock) No light</t>
+  </si>
+  <si>
+    <t>37.50"*18"*39"h</t>
+  </si>
+  <si>
+    <t>DP 13</t>
+  </si>
+  <si>
+    <t>Display Glass Counter show case (with lock) No light</t>
+  </si>
+  <si>
+    <t>DP 14</t>
+  </si>
+  <si>
+    <t>Tall showcase (without lock) No light</t>
+  </si>
+  <si>
+    <t>37.50"*18"*84"h</t>
+  </si>
+  <si>
+    <t>DP 14A</t>
+  </si>
+  <si>
+    <t>Tall showcase (with lock) No light</t>
+  </si>
+  <si>
+    <t>Brochure stand (Brochure Rack)</t>
+  </si>
+  <si>
+    <t>Folding catalogue display stand</t>
+  </si>
+  <si>
+    <t>High power pedestal fan</t>
+  </si>
+  <si>
+    <t>1m*10"</t>
+  </si>
+  <si>
+    <t>Spotlight / 50W LED fixture</t>
+  </si>
+  <si>
+    <t>Plasma with Stand 32 INCH</t>
+  </si>
+  <si>
+    <t>32-inch display with floor stand</t>
+  </si>
+  <si>
+    <t>Garment stand (Single rod)</t>
+  </si>
+  <si>
+    <t>4.5'w*5.5'ht</t>
+  </si>
+  <si>
+    <t>DP 27A</t>
+  </si>
+  <si>
+    <t>Garment stand (Double rod)</t>
+  </si>
+  <si>
+    <t>DP 29</t>
+  </si>
+  <si>
+    <t>Receptionist</t>
+  </si>
+  <si>
+    <t>Professional stall receptionist / hostess (per day)</t>
+  </si>
+  <si>
+    <t>DP 28</t>
+  </si>
+  <si>
+    <t>Mannequin</t>
+  </si>
+  <si>
+    <t>Full-body garment display mannequin</t>
   </si>
 </sst>
 </file>
@@ -334,7 +445,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -357,13 +468,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -406,13 +552,40 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -604,37 +777,48 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>297180</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>982980</xdr:rowOff>
+      <xdr:colOff>307181</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1307306</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="cc0f2cc1-6e27-43c8-bef2-6ba84888391a">
+        <xdr:cNvPr id="3" name="Pic_DP 01">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66CDBC82-6FC6-4CD7-A47C-850F3CA026E1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC50F950-E8D8-C79A-14D1-8EAF469B78DF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4526280" y="1165860"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1207294" y="636588"/>
+          <a:ext cx="1000125" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -642,38 +826,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>297180</xdr:colOff>
+      <xdr:colOff>311385</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1303101</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="50d9baad-b5c3-4388-8336-ba3cd927295e">
+        <xdr:cNvPr id="6" name="Pic_DP 02">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46276051-0AC0-49D9-90E0-78DB6811DEBC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A4ECAB1-6816-18B7-0B10-B959DF7B9BA0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4526280" y="2004060"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1211498" y="1460500"/>
+          <a:ext cx="991716" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -681,38 +876,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>129540</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>754380</xdr:rowOff>
+      <xdr:colOff>406633</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1207854</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="3ab8a5b6-b4ac-49ef-bebc-3e615312be6f">
+        <xdr:cNvPr id="9" name="Pic_DP 03">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BA34FB8-F274-4DB9-8ADF-D0EBF1EEA431}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDB191D3-99FD-C593-D31E-9522E92A74AC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4358640" y="2727960"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1306746" y="2284413"/>
+          <a:ext cx="801221" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -720,38 +926,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:colOff>432851</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1181636</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="d8c09a8f-bc89-44b3-a01c-5c3b5dd9f10d">
+        <xdr:cNvPr id="11" name="Pic_DP 04">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9810D476-6C01-47D9-8DD9-DD9E2CDFD567}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5A9ED2D-342D-023A-9FAF-9F41DFB72C50}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4381500" y="3512820"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1332964" y="3108325"/>
+          <a:ext cx="748785" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -759,38 +976,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>167640</xdr:colOff>
+      <xdr:colOff>393143</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>236220</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1221344</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="7d72b60b-b8d1-4403-ba90-f7a88661b703">
+        <xdr:cNvPr id="14" name="Pic_DP 05">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DF17408-D50B-42CC-8F2A-533ADA7D7EBD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C12E7AC1-CCBA-7353-B15A-24428B218F42}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4396740" y="4457700"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1293256" y="3932238"/>
+          <a:ext cx="828201" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -798,38 +1026,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
+      <xdr:colOff>510579</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1103907</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="2143ea4a-d3ab-4c06-a876-e78cbcb3a62e">
+        <xdr:cNvPr id="17" name="Pic_DP 06">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2759BDF-5359-470F-AF7C-6D370B842473}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C197FA97-31F3-A7B2-0A41-4B713F006A1E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4488180" y="5257800"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1410692" y="4756150"/>
+          <a:ext cx="593328" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -837,38 +1076,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
+      <xdr:colOff>325702</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1288785</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="e9bab8cd-cd6f-4924-9fcc-398bc3ede123">
+        <xdr:cNvPr id="19" name="Pic_DP 08">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9355214-7DE8-4719-8D06-5AE95690F514}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{224CA41B-DC4F-B09B-2592-D6BEBA7BA0F7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4503420" y="6187440"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1225815" y="5580063"/>
+          <a:ext cx="963083" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -876,38 +1126,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
+      <xdr:colOff>240029</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1374458</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="fb5b121a-f6ed-41bc-aaa2-32184b1b4c62">
+        <xdr:cNvPr id="22" name="Pic_DP 09">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CA76EF3-6C62-40D2-9CF5-C01FAB251F77}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{837E3289-0F24-7E8A-E0F0-8E64CDD841F2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4503420" y="8077200"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1140142" y="6403975"/>
+          <a:ext cx="1134429" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -915,38 +1176,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>243840</xdr:colOff>
+      <xdr:colOff>246988</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>236220</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1367498</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="fa1829dd-e353-4446-8403-2dd84bf3cea0">
+        <xdr:cNvPr id="25" name="Pic_DP 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{342E0BB6-0ACD-4FE4-A7E3-0A6FAFA7B713}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C0EBF35-E4AB-D265-0C6F-EF7BAE3C45AF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4472940" y="9349740"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1147101" y="7227888"/>
+          <a:ext cx="1120510" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -954,38 +1226,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>327660</xdr:colOff>
+      <xdr:colOff>139827</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>350520</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1474661</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="67a9715a-0374-4cbf-915b-6a13c25d5e73">
+        <xdr:cNvPr id="27" name="Pic_DP 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1094C83A-1746-4C0B-B62D-B3744A8B08F3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AEDE77F-35F4-1CBD-6EB1-5D3FABF48202}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4556760" y="10721340"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1039940" y="8051800"/>
+          <a:ext cx="1334834" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -993,38 +1276,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>331527</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1282960</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="4914dc83-f6df-42fa-ac62-09577c43981b">
+        <xdr:cNvPr id="30" name="Pic_DP 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{785AEFD0-8936-4792-96DD-95F9B5714620}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0319D461-BEB2-E8F0-C86C-97B956454946}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="731520" y="15567660"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1231640" y="8875713"/>
+          <a:ext cx="951433" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1032,38 +1326,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>379206</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1235280</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="0f7b9bb9-4fb7-46ea-9b91-66f3768a6355">
+        <xdr:cNvPr id="34" name="Pic_DP 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D520B6D2-D569-4739-A978-990B4C7314EB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5682AED0-4981-5989-7D39-3834521FEA66}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="731520" y="16497300"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1279319" y="9699625"/>
+          <a:ext cx="856074" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1071,38 +1376,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>320040</xdr:colOff>
+      <xdr:colOff>516417</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1098069</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="270156c7-5720-4cfd-9fa2-da41ccc2ff72">
+        <xdr:cNvPr id="37" name="Pic_DP 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0FA3B5C-5E54-4341-BB24-10938521A34F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48666442-8D2D-5662-0E7F-82A68FCF3C7A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4549140" y="14257020"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1416530" y="10523538"/>
+          <a:ext cx="581652" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1110,38 +1426,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>167640</xdr:colOff>
+      <xdr:colOff>516417</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1098069</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="1c952b9e-bb9b-45b5-bb5f-395cfc45b2ae">
+        <xdr:cNvPr id="41" name="Pic_DP 14A">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{044ECB89-B50E-4185-9EAA-A706B3ABF8B4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD463818-B114-34CD-79E3-5B529C372A8A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4396740" y="15651480"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1416530" y="11347450"/>
+          <a:ext cx="581652" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1149,38 +1476,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>198120</xdr:colOff>
+      <xdr:colOff>655481</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>959006</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="ec17ea3e-6f31-410b-8d6a-b0cccfc627fe">
+        <xdr:cNvPr id="44" name="Pic_DP 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{362A5968-0503-4FD1-B3CF-6272D46E63E4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{955EC4B9-A8FE-B9CB-AD38-DB122EC1730A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4427220" y="16771620"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1555594" y="12171363"/>
+          <a:ext cx="303525" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1188,38 +1526,49 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
+      <xdr:colOff>325702</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>251460</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="857250"/>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1288785</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="39cdcd46-40ea-4cd5-aa02-0ed909ab1455">
+        <xdr:cNvPr id="46" name="Pic_DP 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B111DE5-CCDC-40E0-8DAB-764497670708}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA8CA07C-43E0-63EA-43CF-E8291E0B5C82}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4572000" y="17952720"/>
-          <a:ext cx="1143000" cy="857250"/>
+          <a:off x="1225815" y="12995275"/>
+          <a:ext cx="963083" cy="722313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1227,13 +1576,463 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>356286</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1258201</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Pic_DP 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D8CA68C-AB5D-E73C-5E13-0C1F6D9A0C07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1256399" y="13819188"/>
+          <a:ext cx="901915" cy="722313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>325702</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1288785</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Pic_DP 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A1E087C-420B-59F2-E1D3-E532E3895959}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1225815" y="14643100"/>
+          <a:ext cx="963083" cy="722313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>325702</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1288785</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Pic_DP 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB4C2E62-B585-3ECD-AFCB-EDEEECEC09A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1225815" y="15467013"/>
+          <a:ext cx="963083" cy="722313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>325702</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1288785</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Pic_DP 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1426E48B-9A39-F96B-5826-77B6E619BB11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1225815" y="16290925"/>
+          <a:ext cx="963083" cy="722313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>325702</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1288785</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Pic_DP 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3F2E63C-660E-65D7-E694-F241B5E59DDF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1225815" y="17114838"/>
+          <a:ext cx="963083" cy="722313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>453731</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1160756</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Pic_DP 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F07FA5AF-9CA6-CC7E-63E5-69BD285F7FC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1353844" y="17938750"/>
+          <a:ext cx="707025" cy="722313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>453938</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1160548</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Pic_DP 27A">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{619134D8-8309-83F9-C26D-F8DF147D0966}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1354051" y="18762663"/>
+          <a:ext cx="706610" cy="722313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>446087</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1168400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Pic_DP 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2523948E-7504-2D99-955B-52B48C1E88E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1346200" y="19586575"/>
+          <a:ext cx="722313" cy="722313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>566205</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1048282</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>773113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Pic_DP 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C68CB4F8-A5D3-97B1-13E6-D130BD1EF4F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1466318" y="20410488"/>
+          <a:ext cx="482077" cy="722313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ADD95150-6E25-40FA-AAB6-13A6FD0FD01D}" name="HireChargesTable" displayName="HireChargesTable" ref="A2:G18" totalsRowShown="0" headerRowDxfId="7">
-  <autoFilter ref="A2:G18" xr:uid="{ADD95150-6E25-40FA-AAB6-13A6FD0FD01D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ADD95150-6E25-40FA-AAB6-13A6FD0FD01D}" name="HireChargesTable" displayName="HireChargesTable" ref="A2:G27" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="A2:G27" xr:uid="{ADD95150-6E25-40FA-AAB6-13A6FD0FD01D}"/>
   <tableColumns count="7">
     <tableColumn id="2" xr3:uid="{ABBCDBE1-F530-4F25-A95D-1274CA8D0D5A}" name="Item Code" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{D0F7E117-C148-44FD-B1A0-BE1F39B6385D}" name="Product Image(NOTE REFRENCE IMAGES ARE THERE .FINAL PRODUCT COULD CHANGE )" dataDxfId="5"/>
@@ -1791,49 +2590,49 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{326B6254-0BD8-4464-A2A5-514480A20D8C}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="61.6640625" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="20.46484375" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="11.53125" customWidth="1"/>
-    <col min="7" max="7" width="14.19921875" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.59765625" customWidth="1"/>
+    <col min="3" max="3" width="32.59765625" customWidth="1"/>
+    <col min="4" max="4" width="28.59765625" customWidth="1"/>
+    <col min="5" max="5" width="20.59765625" customWidth="1"/>
+    <col min="6" max="7" width="14.59765625" customWidth="1"/>
+    <col min="8" max="8" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="15">
-        <f>COUNTA(A3:A18)</f>
-        <v>16</v>
+      <c r="A1" s="24">
+        <f>COUNTA(A3:A27)</f>
+        <v>25</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" s="15">
-        <f>COUNT(E3:E18)</f>
-        <v>16</v>
+        <v>43</v>
+      </c>
+      <c r="D1" s="24">
+        <f>COUNT(E3:E27)</f>
+        <v>25</v>
       </c>
       <c r="E1" s="15"/>
       <c r="F1" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" s="15">
-        <f>COUNT(F3:F18)</f>
-        <v>16</v>
+        <v>44</v>
+      </c>
+      <c r="G1" s="24">
+        <f>COUNT(F3:F27)</f>
+        <v>25</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="55.5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="32" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>17</v>
@@ -1842,343 +2641,565 @@
         <v>18</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H2" s="14"/>
     </row>
-    <row r="3" spans="1:8" ht="58.25" customHeight="1">
+    <row r="3" spans="1:8" ht="65" customHeight="1">
       <c r="A3" s="17" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="20">
+        <v>52</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="21">
         <v>600</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="22">
         <v>7</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="14"/>
-    </row>
-    <row r="4" spans="1:8" ht="60" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" ht="65" customHeight="1">
       <c r="A4" s="17" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="20">
-        <v>1400</v>
-      </c>
-      <c r="F4" s="21">
-        <v>15</v>
+        <v>55</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="21">
+        <v>400</v>
+      </c>
+      <c r="F4" s="22">
+        <v>5</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:8" ht="61.25" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H4" s="23"/>
+    </row>
+    <row r="5" spans="1:8" ht="65" customHeight="1">
       <c r="A5" s="17" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="20">
-        <v>700</v>
-      </c>
-      <c r="F5" s="21">
-        <v>8</v>
+        <v>21</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="21">
+        <v>1400</v>
+      </c>
+      <c r="F5" s="22">
+        <v>15</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:8" ht="55.8" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H5" s="23"/>
+    </row>
+    <row r="6" spans="1:8" ht="65" customHeight="1">
       <c r="A6" s="17" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="20">
+        <v>58</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="21">
         <v>700</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="22">
         <v>8</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:8" ht="78" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H6" s="23"/>
+    </row>
+    <row r="7" spans="1:8" ht="65" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20">
-        <v>3000</v>
-      </c>
-      <c r="F7" s="21">
-        <v>33</v>
+        <v>60</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="21">
+        <v>700</v>
+      </c>
+      <c r="F7" s="22">
+        <v>8</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" spans="1:8" ht="69.599999999999994" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H7" s="23"/>
+    </row>
+    <row r="8" spans="1:8" ht="65" customHeight="1">
       <c r="A8" s="17" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="20">
-        <v>5000</v>
-      </c>
-      <c r="F8" s="21">
-        <v>55</v>
+        <v>63</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="21">
+        <v>500</v>
+      </c>
+      <c r="F8" s="22">
+        <v>6</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" spans="1:8" ht="84" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H8" s="23"/>
+    </row>
+    <row r="9" spans="1:8" ht="65" customHeight="1">
       <c r="A9" s="17" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="21">
+        <v>3000</v>
+      </c>
+      <c r="F9" s="22">
         <v>33</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="20">
-        <v>6000</v>
-      </c>
-      <c r="F9" s="21">
+      <c r="G9" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="23"/>
+    </row>
+    <row r="10" spans="1:8" ht="65" customHeight="1">
+      <c r="A10" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="G9" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="1:8" ht="95.45" customHeight="1">
-      <c r="A10" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="20">
-        <v>1200</v>
-      </c>
-      <c r="F10" s="21">
-        <v>13</v>
+      <c r="D10" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="21">
+        <v>5000</v>
+      </c>
+      <c r="F10" s="22">
+        <v>55</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:8" ht="99" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H10" s="23"/>
+    </row>
+    <row r="11" spans="1:8" ht="65" customHeight="1">
       <c r="A11" s="17" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="20">
-        <v>1500</v>
-      </c>
-      <c r="F11" s="21">
-        <v>16</v>
+        <v>68</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="21">
+        <v>6000</v>
+      </c>
+      <c r="F11" s="22">
+        <v>66</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:8" ht="117" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H11" s="23"/>
+    </row>
+    <row r="12" spans="1:8" ht="65" customHeight="1">
       <c r="A12" s="17" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="20">
-        <v>1500</v>
-      </c>
-      <c r="F12" s="21">
-        <v>16</v>
+        <v>70</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="21">
+        <v>1200</v>
+      </c>
+      <c r="F12" s="22">
+        <v>13</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:8" ht="88.25" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H12" s="23"/>
+    </row>
+    <row r="13" spans="1:8" ht="65" customHeight="1">
       <c r="A13" s="17" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="20">
-        <v>600</v>
-      </c>
-      <c r="F13" s="21">
-        <v>6</v>
+        <v>73</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="21">
+        <v>2500</v>
+      </c>
+      <c r="F13" s="22">
+        <v>28</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14" spans="1:8" ht="79.8" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H13" s="23"/>
+    </row>
+    <row r="14" spans="1:8" ht="65" customHeight="1">
       <c r="A14" s="17" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="20">
-        <v>500</v>
-      </c>
-      <c r="F14" s="21">
-        <v>5</v>
+        <v>76</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="21">
+        <v>3000</v>
+      </c>
+      <c r="F14" s="22">
+        <v>33</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:8" ht="121.25" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H14" s="23"/>
+    </row>
+    <row r="15" spans="1:8" ht="65" customHeight="1">
       <c r="A15" s="17" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="21">
+        <v>4000</v>
+      </c>
+      <c r="F15" s="22">
         <v>44</v>
       </c>
-      <c r="E15" s="20">
-        <v>250</v>
-      </c>
-      <c r="F15" s="21">
-        <v>3</v>
-      </c>
       <c r="G15" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16" spans="1:8" ht="90.6" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H15" s="23"/>
+    </row>
+    <row r="16" spans="1:8" ht="65" customHeight="1">
       <c r="A16" s="17" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="20">
-        <v>1500</v>
-      </c>
-      <c r="F16" s="21">
-        <v>13</v>
+        <v>81</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="21">
+        <v>5000</v>
+      </c>
+      <c r="F16" s="22">
+        <v>55</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="1:8" ht="80.45" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H16" s="23"/>
+    </row>
+    <row r="17" spans="1:8" ht="65" customHeight="1">
       <c r="A17" s="17" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="20">
-        <v>3500</v>
-      </c>
-      <c r="F17" s="21">
-        <v>27</v>
+        <v>82</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="21">
+        <v>1500</v>
+      </c>
+      <c r="F17" s="22">
+        <v>16</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="1:8" ht="105.6" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H17" s="23"/>
+    </row>
+    <row r="18" spans="1:8" ht="65" customHeight="1">
       <c r="A18" s="17" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B18" s="18"/>
       <c r="C18" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="21">
+        <v>1500</v>
+      </c>
+      <c r="F18" s="22">
+        <v>16</v>
+      </c>
+      <c r="G18" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="20">
+      <c r="H18" s="23"/>
+    </row>
+    <row r="19" spans="1:8" ht="65" customHeight="1">
+      <c r="A19" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="26"/>
+      <c r="C19" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="28">
+        <v>600</v>
+      </c>
+      <c r="F19" s="28">
+        <v>6</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="30"/>
+    </row>
+    <row r="20" spans="1:8" ht="65" customHeight="1">
+      <c r="A20" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="26"/>
+      <c r="C20" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="28">
+        <v>500</v>
+      </c>
+      <c r="F20" s="28">
+        <v>5</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="30"/>
+    </row>
+    <row r="21" spans="1:8" ht="65" customHeight="1">
+      <c r="A21" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="26"/>
+      <c r="C21" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="28">
+        <v>250</v>
+      </c>
+      <c r="F21" s="28">
+        <v>3</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" s="30"/>
+    </row>
+    <row r="22" spans="1:8" ht="65" customHeight="1">
+      <c r="A22" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="26"/>
+      <c r="C22" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="28">
+        <v>1500</v>
+      </c>
+      <c r="F22" s="28">
+        <v>13</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" s="30"/>
+    </row>
+    <row r="23" spans="1:8" ht="65" customHeight="1">
+      <c r="A23" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="26"/>
+      <c r="C23" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="28">
+        <v>3500</v>
+      </c>
+      <c r="F23" s="28">
+        <v>27</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="30"/>
+    </row>
+    <row r="24" spans="1:8" ht="65" customHeight="1">
+      <c r="A24" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="26"/>
+      <c r="C24" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="28">
         <v>900</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F24" s="28">
         <v>7</v>
       </c>
-      <c r="G18" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" s="14"/>
+      <c r="G24" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H24" s="30"/>
+    </row>
+    <row r="25" spans="1:8" ht="65" customHeight="1">
+      <c r="A25" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="26"/>
+      <c r="C25" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="28">
+        <v>900</v>
+      </c>
+      <c r="F25" s="28">
+        <v>7</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="30"/>
+    </row>
+    <row r="26" spans="1:8" ht="65" customHeight="1">
+      <c r="A26" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="26"/>
+      <c r="C26" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="28">
+        <v>1500</v>
+      </c>
+      <c r="F26" s="28">
+        <v>16</v>
+      </c>
+      <c r="G26" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="30"/>
+    </row>
+    <row r="27" spans="1:8" ht="65" customHeight="1">
+      <c r="A27" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="28">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="28">
+        <v>12</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
